--- a/buildplan_generator/output/25-085 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-085 GENERATED BUILD PLAN.xlsx
@@ -74,8 +74,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
-        <bgColor rgb="00FCE4EC"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -86,8 +86,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-004, 25-003, 25-013, 25-015, 25-021</t>
+          <t>25-039, 25-025, 25-037, 23-098, 25-026</t>
         </is>
       </c>
     </row>
@@ -635,17 +635,15 @@
         </is>
       </c>
       <c r="E6" s="8" t="n"/>
-      <c r="F6" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -673,12 +671,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -722,17 +720,17 @@
       <c r="E9" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <v>0.5</v>
+      <c r="F9" s="9" t="n">
+        <v>4.4</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>0.5-0.5</t>
+          <t>ratio=1.10 (1.08-1.20)</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -759,8 +757,8 @@
       <c r="E10" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F10" s="11" t="n">
-        <v>1</v>
+      <c r="F10" s="9" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -769,7 +767,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>1.0-7.5</t>
+          <t>ratio=1.36 (0.29-1.82)</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -796,17 +794,17 @@
       <c r="E11" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="F11" s="11" t="n">
-        <v>5</v>
+      <c r="F11" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>3.5-6.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -838,12 +836,12 @@
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-7.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -870,17 +868,17 @@
       <c r="E13" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="10" t="n">
-        <v>1.5</v>
+      <c r="F13" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -907,17 +905,17 @@
       <c r="E14" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F14" s="10" t="n">
+      <c r="F14" s="9" t="n">
         <v>2</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -944,17 +942,17 @@
       <c r="E15" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F15" s="10" t="n">
-        <v>5</v>
+      <c r="F15" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>5.0-5.0</t>
+          <t>ratio=1.50 (1.00-2.00)</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -981,17 +979,17 @@
       <c r="E16" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F16" s="10" t="n">
-        <v>2</v>
+      <c r="F16" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=2.00 (1.00-2.00)</t>
         </is>
       </c>
       <c r="I16" s="8" t="n"/>
@@ -1035,8 +1033,8 @@
       <c r="E18" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="F18" s="11" t="n">
-        <v>17</v>
+      <c r="F18" s="9" t="n">
+        <v>42.5</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
@@ -1045,7 +1043,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>12.5-35.0</t>
+          <t>ratio=1.06 (0.86-1.50)</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1072,8 +1070,8 @@
       <c r="E19" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F19" s="11" t="n">
-        <v>8</v>
+      <c r="F19" s="9" t="n">
+        <v>18.3</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1082,7 +1080,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>4.0-13.0</t>
+          <t>ratio=0.92 (0.79-1.10)</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1126,8 +1124,8 @@
       <c r="E21" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F21" s="11" t="n">
-        <v>4</v>
+      <c r="F21" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1136,7 +1134,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>3.0-5.0</t>
+          <t>ratio=0.75 (0.75-1.10)</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1180,7 +1178,7 @@
       <c r="E23" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F23" s="11" t="n">
+      <c r="F23" s="9" t="n">
         <v>2</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -1190,7 +1188,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (0.50-1.00)</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1217,7 +1215,7 @@
       <c r="E24" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" s="9" t="n">
         <v>3</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
@@ -1227,7 +1225,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>3.0-4.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1272,12 +1270,12 @@
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1304,8 +1302,8 @@
       <c r="E27" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="F27" s="11" t="n">
-        <v>4</v>
+      <c r="F27" s="9" t="n">
+        <v>21</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1314,7 +1312,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>3.0-17.0</t>
+          <t>ratio=0.75 (0.67-1.09)</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1341,8 +1339,8 @@
       <c r="E28" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F28" s="11" t="n">
-        <v>5</v>
+      <c r="F28" s="9" t="n">
+        <v>21.4</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1351,7 +1349,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>3.0-10.0</t>
+          <t>ratio=1.07 (0.62-1.36)</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1395,8 +1393,8 @@
       <c r="E30" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F30" s="11" t="n">
-        <v>6.5</v>
+      <c r="F30" s="9" t="n">
+        <v>8.300000000000001</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
@@ -1405,7 +1403,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>4.0-7.0</t>
+          <t>ratio=0.69 (0.56-1.20)</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1430,17 +1428,15 @@
         </is>
       </c>
       <c r="E31" s="8" t="n"/>
-      <c r="F31" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1467,17 +1463,17 @@
       <c r="E32" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F32" s="10" t="n">
-        <v>2.5</v>
+      <c r="F32" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>1.5-3.5</t>
+          <t>ratio=2.50 (1.00-5.00)</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1504,8 +1500,8 @@
       <c r="E33" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F33" s="11" t="n">
-        <v>2</v>
+      <c r="F33" s="9" t="n">
+        <v>3.3</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1514,7 +1510,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>1.0-4.0</t>
+          <t>ratio=0.83 (0.50-1.17)</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1541,8 +1537,8 @@
       <c r="E34" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F34" s="11" t="n">
-        <v>2.5</v>
+      <c r="F34" s="9" t="n">
+        <v>7.5</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
@@ -1551,7 +1547,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>2.0-4.0</t>
+          <t>ratio=0.94 (0.58-1.19)</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1578,8 +1574,8 @@
       <c r="E35" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F35" s="11" t="n">
-        <v>5.5</v>
+      <c r="F35" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1588,7 +1584,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>3.5-6.0</t>
+          <t>ratio=0.50 (0.50-0.67)</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1632,8 +1628,8 @@
       <c r="E37" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F37" s="11" t="n">
-        <v>5</v>
+      <c r="F37" s="9" t="n">
+        <v>6.7</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -1642,7 +1638,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>3.0-13.0</t>
+          <t>ratio=0.83 (0.83-0.88)</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1687,12 +1683,12 @@
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1719,8 +1715,8 @@
       <c r="E40" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="F40" s="11" t="n">
-        <v>13</v>
+      <c r="F40" s="9" t="n">
+        <v>13.2</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1729,7 +1725,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>5.0-34.0</t>
+          <t>ratio=0.88 (0.38-1.15)</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1756,8 +1752,8 @@
       <c r="E41" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F41" s="11" t="n">
-        <v>10</v>
+      <c r="F41" s="9" t="n">
+        <v>16</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -1766,7 +1762,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>4.5-11.5</t>
+          <t>ratio=1.33 (0.67-1.67)</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1793,8 +1789,8 @@
       <c r="E42" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="F42" s="11" t="n">
-        <v>4</v>
+      <c r="F42" s="9" t="n">
+        <v>11.7</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
@@ -1803,7 +1799,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>4.0-6.0</t>
+          <t>ratio=1.17 (0.33-2.00)</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1830,8 +1826,8 @@
       <c r="E43" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F43" s="11" t="n">
-        <v>6.5</v>
+      <c r="F43" s="9" t="n">
+        <v>6.9</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1840,7 +1836,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>4.0-8.0</t>
+          <t>ratio=1.38 (0.75-2.40)</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1867,8 +1863,8 @@
       <c r="E44" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F44" s="11" t="n">
-        <v>5.5</v>
+      <c r="F44" s="9" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1877,7 +1873,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>4.5-8.0</t>
+          <t>ratio=1.38 (1.12-1.60)</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1904,8 +1900,8 @@
       <c r="E45" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F45" s="11" t="n">
-        <v>2</v>
+      <c r="F45" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
@@ -1914,7 +1910,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>1.0-4.0</t>
+          <t>ratio=1.00 (0.83-1.00)</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1939,17 +1935,15 @@
         </is>
       </c>
       <c r="E46" s="8" t="n"/>
-      <c r="F46" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1976,8 +1970,8 @@
       <c r="E47" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="F47" s="11" t="n">
-        <v>8.800000000000001</v>
+      <c r="F47" s="9" t="n">
+        <v>9</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1986,7 +1980,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>8.0-10.0</t>
+          <t>ratio=1.00 (0.62-1.33)</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2013,8 +2007,8 @@
       <c r="E48" s="8" t="n">
         <v>14</v>
       </c>
-      <c r="F48" s="11" t="n">
-        <v>8.199999999999999</v>
+      <c r="F48" s="9" t="n">
+        <v>14</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -2023,7 +2017,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>5.5-17.0</t>
+          <t>ratio=1.00 (0.64-1.43)</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2050,8 +2044,8 @@
       <c r="E49" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F49" s="11" t="n">
-        <v>8.800000000000001</v>
+      <c r="F49" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
@@ -2060,7 +2054,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>1.0-11.8</t>
+          <t>ratio=1.50 (0.50-3.25)</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2104,17 +2098,17 @@
       <c r="E51" s="8" t="n">
         <v>39</v>
       </c>
-      <c r="F51" s="9" t="n">
-        <v>24</v>
+      <c r="F51" s="10" t="n">
+        <v>27.3</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-129.8</t>
+          <t>ratio=0.70 (n=1)</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2141,17 +2135,17 @@
       <c r="E52" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F52" s="11" t="n">
-        <v>3</v>
+      <c r="F52" s="10" t="n">
+        <v>3.5</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>1.0-4.0</t>
+          <t>ratio=0.71 (n=2)</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2178,8 +2172,8 @@
       <c r="E53" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F53" s="11" t="n">
-        <v>10</v>
+      <c r="F53" s="9" t="n">
+        <v>2.2</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
@@ -2188,7 +2182,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>2.0-11.0</t>
+          <t>ratio=0.43 (0.36-0.73)</t>
         </is>
       </c>
       <c r="I53" s="8" t="n"/>
@@ -2215,8 +2209,8 @@
       <c r="E54" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="F54" s="11" t="n">
-        <v>15.2</v>
+      <c r="F54" s="9" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -2225,7 +2219,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>13.5-36.0</t>
+          <t>ratio=0.55 (0.33-0.72)</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2252,8 +2246,8 @@
       <c r="E55" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F55" s="11" t="n">
-        <v>24.8</v>
+      <c r="F55" s="9" t="n">
+        <v>4.2</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
@@ -2262,7 +2256,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>1.5-41.5</t>
+          <t>ratio=0.71 (0.50-0.75)</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2287,17 +2281,15 @@
         </is>
       </c>
       <c r="E56" s="8" t="n"/>
-      <c r="F56" s="9" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>global:0.5-2.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2324,7 +2316,7 @@
       <c r="E57" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F57" s="11" t="n">
+      <c r="F57" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G57" s="8" t="inlineStr">
@@ -2334,7 +2326,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.5</t>
+          <t>ratio=1.00 (0.50-1.00)</t>
         </is>
       </c>
       <c r="I57" s="8" t="n"/>
@@ -2378,17 +2370,17 @@
       <c r="E59" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F59" s="10" t="n">
-        <v>1.8</v>
+      <c r="F59" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.5</t>
+          <t>ratio=0.88 (0.50-1.00)</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2413,17 +2405,15 @@
         </is>
       </c>
       <c r="E60" s="8" t="n"/>
-      <c r="F60" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2448,17 +2438,15 @@
         </is>
       </c>
       <c r="E61" s="8" t="n"/>
-      <c r="F61" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>global:2.0-2.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I61" s="8" t="n"/>
@@ -2486,12 +2474,12 @@
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2535,8 +2523,8 @@
       <c r="E64" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F64" s="11" t="n">
-        <v>3</v>
+      <c r="F64" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
@@ -2545,7 +2533,7 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>1.0-4.0</t>
+          <t>ratio=3.00 (0.50-4.12)</t>
         </is>
       </c>
       <c r="I64" s="8" t="n"/>
@@ -2572,8 +2560,8 @@
       <c r="E65" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F65" s="11" t="n">
-        <v>9</v>
+      <c r="F65" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
@@ -2582,7 +2570,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>8.0-36.5</t>
+          <t>ratio=1.25 (0.90-1.90)</t>
         </is>
       </c>
       <c r="I65" s="8" t="n"/>
@@ -2610,12 +2598,12 @@
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -2643,12 +2631,12 @@
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -2675,8 +2663,8 @@
       <c r="E68" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="F68" s="11" t="n">
-        <v>51.5</v>
+      <c r="F68" s="9" t="n">
+        <v>45</v>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
@@ -2685,7 +2673,7 @@
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>16.0-84.0</t>
+          <t>ratio=1.12 (0.50-1.60)</t>
         </is>
       </c>
       <c r="I68" s="8" t="n"/>
@@ -2713,12 +2701,12 @@
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I69" s="8" t="n"/>
@@ -2746,12 +2734,12 @@
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I70" s="8" t="n"/>
@@ -2779,12 +2767,12 @@
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I71" s="8" t="n"/>
@@ -2828,17 +2816,17 @@
       <c r="E73" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F73" s="11" t="n">
-        <v>3</v>
+      <c r="F73" s="10" t="n">
+        <v>2.5</v>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>2.5-12.0</t>
+          <t>ratio=1.25 (n=2)</t>
         </is>
       </c>
       <c r="I73" s="8" t="n"/>
@@ -2865,17 +2853,17 @@
       <c r="E74" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F74" s="10" t="n">
-        <v>3.5</v>
+      <c r="F74" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>3.5-3.5</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I74" s="8" t="n"/>
@@ -2903,12 +2891,12 @@
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I75" s="8" t="n"/>
@@ -2935,8 +2923,8 @@
       <c r="E76" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F76" s="11" t="n">
-        <v>3.5</v>
+      <c r="F76" s="9" t="n">
+        <v>7</v>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
@@ -2945,7 +2933,7 @@
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>3.0-17.0</t>
+          <t>ratio=1.75 (0.33-2.25)</t>
         </is>
       </c>
       <c r="I76" s="8" t="n"/>
@@ -2959,7 +2947,7 @@
         </is>
       </c>
       <c r="F78" s="1" t="n">
-        <v>315.3</v>
+        <v>397.9</v>
       </c>
     </row>
   </sheetData>
@@ -3027,7 +3015,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-004, 25-003, 25-013, 25-015, 25-021</t>
+          <t>25-039, 25-025, 25-037, 23-098, 25-026</t>
         </is>
       </c>
     </row>
@@ -4897,35 +4885,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25-004</t>
+          <t>25-039</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25-003</t>
+          <t>25-025</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25-013</t>
+          <t>25-037</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25-015</t>
+          <t>23-098</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25-021</t>
+          <t>25-026</t>
         </is>
       </c>
     </row>
@@ -4980,23 +4968,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5014,19 +4998,15 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>25-003, 25-004, 25-013, 25-015</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5040,21 +5020,21 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.5-0.5</t>
+          <t>ratio=1.10 (1.08-1.20)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5050,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5079,12 +5059,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.0-7.5</t>
+          <t>ratio=1.36 (0.29-1.82)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -5100,21 +5080,21 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3.5-6.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013</t>
+          <t>25-039</t>
         </is>
       </c>
     </row>
@@ -5134,17 +5114,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>global:1.0-7.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -5160,21 +5140,21 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-013, 25-004, 25-003</t>
+          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -5194,17 +5174,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-004, 25-003</t>
+          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -5220,21 +5200,21 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5.0-5.0</t>
+          <t>ratio=1.50 (1.00-2.00)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-004, 25-003</t>
+          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -5250,21 +5230,21 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=2.00 (1.00-2.00)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-015, 25-013, 25-004, 25-003</t>
+          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -5280,7 +5260,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>17</v>
+        <v>42.5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5289,12 +5269,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>12.5-35.0</t>
+          <t>ratio=1.06 (0.86-1.50)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5290,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8</v>
+        <v>18.3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5319,12 +5299,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>4.0-13.0</t>
+          <t>ratio=0.92 (0.79-1.10)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5320,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5349,12 +5329,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3.0-5.0</t>
+          <t>ratio=0.75 (0.75-1.10)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -5379,12 +5359,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (0.50-1.00)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -5409,12 +5389,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3.0-4.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -5434,19 +5414,15 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>25-003, 25-004, 25-013, 25-015, 25-021</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5460,7 +5436,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5469,12 +5445,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3.0-17.0</t>
+          <t>ratio=0.75 (0.67-1.09)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5466,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5</v>
+        <v>21.4</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5499,12 +5475,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3.0-10.0</t>
+          <t>ratio=1.07 (0.62-1.36)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5496,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5529,12 +5505,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4.0-7.0</t>
+          <t>ratio=0.69 (0.56-1.20)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013</t>
+          <t>25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -5550,23 +5526,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5580,21 +5552,21 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.5-3.5</t>
+          <t>ratio=2.50 (1.00-5.00)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013</t>
+          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5582,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5619,12 +5591,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.0-4.0</t>
+          <t>ratio=0.83 (0.50-1.17)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013</t>
+          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5612,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5649,12 +5621,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2.0-4.0</t>
+          <t>ratio=0.94 (0.58-1.19)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013</t>
+          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -5670,7 +5642,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5679,12 +5651,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3.5-6.0</t>
+          <t>ratio=0.50 (0.50-0.67)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013</t>
+          <t>25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5700,7 +5672,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5709,12 +5681,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3.0-13.0</t>
+          <t>ratio=0.83 (0.83-0.88)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -5730,23 +5702,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5764,19 +5732,15 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>25-015</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5790,7 +5754,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5799,12 +5763,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>5.0-34.0</t>
+          <t>ratio=0.88 (0.38-1.15)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -5820,7 +5784,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5829,12 +5793,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>4.5-11.5</t>
+          <t>ratio=1.33 (0.67-1.67)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013</t>
+          <t>25-039, 25-037, 25-025</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5814,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>11.7</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5859,12 +5823,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4.0-6.0</t>
+          <t>ratio=1.17 (0.33-2.00)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013</t>
+          <t>25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5880,7 +5844,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6.5</v>
+        <v>6.9</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5889,12 +5853,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>4.0-8.0</t>
+          <t>ratio=1.38 (0.75-2.40)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5874,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5919,12 +5883,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4.5-8.0</t>
+          <t>ratio=1.38 (1.12-1.60)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5904,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5949,12 +5913,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.0-4.0</t>
+          <t>ratio=1.00 (0.83-1.00)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-039, 25-037, 25-026</t>
         </is>
       </c>
     </row>
@@ -5970,23 +5934,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6000,7 +5960,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6009,12 +5969,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>8.0-10.0</t>
+          <t>ratio=1.00 (0.62-1.33)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013</t>
+          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -6030,7 +5990,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>8.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6039,12 +5999,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>5.5-17.0</t>
+          <t>ratio=1.00 (0.64-1.43)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -6060,7 +6020,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8.800000000000001</v>
+        <v>3</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6069,12 +6029,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.0-11.8</t>
+          <t>ratio=1.50 (0.50-3.25)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -6090,21 +6050,21 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>24</v>
+        <v>27.3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>global:1.0-129.8</t>
+          <t>ratio=0.70 (n=1)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>23-098</t>
         </is>
       </c>
     </row>
@@ -6120,21 +6080,21 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.0-4.0</t>
+          <t>ratio=0.71 (n=2)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-037, 23-098</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6110,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>10</v>
+        <v>2.2</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6159,12 +6119,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2.0-11.0</t>
+          <t>ratio=0.43 (0.36-0.73)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -6180,7 +6140,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>15.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6189,12 +6149,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>13.5-36.0</t>
+          <t>ratio=0.55 (0.33-0.72)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6170,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>24.8</v>
+        <v>4.2</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6219,12 +6179,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.5-41.5</t>
+          <t>ratio=0.71 (0.50-0.75)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-039, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -6240,23 +6200,19 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>global:0.5-2.0</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6279,12 +6235,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.0-2.5</t>
+          <t>ratio=1.00 (0.50-1.00)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -6300,21 +6256,21 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.0-2.5</t>
+          <t>ratio=0.88 (0.50-1.00)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -6330,23 +6286,19 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6360,23 +6312,19 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>global:2.0-2.0</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6394,19 +6342,15 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>25-015</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6420,7 +6364,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6429,12 +6373,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.0-4.0</t>
+          <t>ratio=3.00 (0.50-4.12)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6394,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6459,12 +6403,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>8.0-36.5</t>
+          <t>ratio=1.25 (0.90-1.90)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -6484,19 +6428,15 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>25-003, 25-004, 25-013, 25-015, 25-021</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6514,19 +6454,15 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>25-015</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6540,7 +6476,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>51.5</v>
+        <v>45</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6549,12 +6485,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>16.0-84.0</t>
+          <t>ratio=1.12 (0.50-1.60)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>
@@ -6574,19 +6510,15 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>25-003, 25-004, 25-013, 25-015, 25-021</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6604,19 +6536,15 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>25-003, 25-004, 25-015</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6634,19 +6562,15 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>25-003, 25-004, 25-015</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6660,21 +6584,21 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2.5-12.0</t>
+          <t>ratio=1.25 (n=2)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-039, 23-098</t>
         </is>
       </c>
     </row>
@@ -6690,21 +6614,21 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>3.5-3.5</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>25-015, 25-013, 25-004, 25-003</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -6724,19 +6648,15 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>25-003, 25-004, 25-013, 25-015, 25-021</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6750,7 +6670,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6759,12 +6679,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>3.0-17.0</t>
+          <t>ratio=1.75 (0.33-2.25)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>25-021, 25-015, 25-013, 25-004, 25-003</t>
+          <t>25-039, 25-026, 25-025, 23-098</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-085 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-085 GENERATED BUILD PLAN.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-039, 25-025, 25-037, 23-098, 25-026</t>
+          <t>25-025, 25-039, 25-037, 25-026, 25-087</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.10 (1.08-1.20)</t>
+          <t>ratio=1.10 (1.00-1.20)</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -804,7 +804,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -989,7 +989,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.00 (1.00-2.00)</t>
+          <t>ratio=2.00 (1.25-2.00)</t>
         </is>
       </c>
       <c r="I16" s="8" t="n"/>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.06 (0.86-1.50)</t>
+          <t>ratio=1.06 (0.29-1.50)</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1071,7 +1071,7 @@
         <v>20</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>18.3</v>
+        <v>20</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.92 (0.79-1.10)</t>
+          <t>ratio=1.00 (0.79-1.33)</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.00)</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.67-1.09)</t>
+          <t>ratio=0.75 (0.67-1.50)</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1340,7 +1340,7 @@
         <v>20</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>21.4</v>
+        <v>20</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.07 (0.62-1.36)</t>
+          <t>ratio=1.00 (0.62-1.36)</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1394,7 +1394,7 @@
         <v>12</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.69 (0.56-1.20)</t>
+          <t>ratio=0.61 (0.56-0.78)</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1501,7 +1501,7 @@
         <v>4</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.83 (0.50-1.17)</t>
+          <t>ratio=0.58 (0.50-1.17)</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1538,7 +1538,7 @@
         <v>8</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.94 (0.58-1.19)</t>
+          <t>ratio=0.88 (0.33-1.19)</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.83 (0.83-0.88)</t>
+          <t>ratio=0.83 (0.83-0.83)</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1716,7 +1716,7 @@
         <v>15</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>13.2</v>
+        <v>10.5</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.38-1.15)</t>
+          <t>ratio=0.70 (0.38-1.15)</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1827,7 +1827,7 @@
         <v>5</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>6.9</v>
+        <v>5</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.38 (0.75-2.40)</t>
+          <t>ratio=1.00 (0.75-1.75)</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1864,7 +1864,7 @@
         <v>6</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.38 (1.12-1.60)</t>
+          <t>ratio=1.25 (1.12-1.50)</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.62-1.33)</t>
+          <t>ratio=1.00 (0.33-1.33)</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2008,7 +2008,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>14</v>
+        <v>16.8</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.64-1.43)</t>
+          <t>ratio=1.20 (0.64-1.43)</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2045,7 +2045,7 @@
         <v>2</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (0.50-3.25)</t>
+          <t>ratio=1.00 (0.50-2.00)</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2099,7 +2099,7 @@
         <v>39</v>
       </c>
       <c r="F51" s="10" t="n">
-        <v>27.3</v>
+        <v>13.9</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.70 (n=1)</t>
+          <t>ratio=0.36 (n=1)</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2136,7 +2136,7 @@
         <v>5</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.71 (n=2)</t>
+          <t>ratio=0.67 (n=1)</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.43 (0.36-0.73)</t>
+          <t>ratio=0.43 (0.33-0.73)</t>
         </is>
       </c>
       <c r="I53" s="8" t="n"/>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.55 (0.33-0.72)</t>
+          <t>ratio=0.55 (0.30-0.72)</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2247,7 +2247,7 @@
         <v>6</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.71 (0.50-0.75)</t>
+          <t>ratio=0.75 (0.67-1.00)</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2371,7 +2371,7 @@
         <v>1</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.50-1.00)</t>
+          <t>ratio=0.75 (0.50-1.00)</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2524,7 +2524,7 @@
         <v>2</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>ratio=3.00 (0.50-4.12)</t>
+          <t>ratio=2.81 (0.50-4.12)</t>
         </is>
       </c>
       <c r="I64" s="8" t="n"/>
@@ -2561,7 +2561,7 @@
         <v>12</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>15</v>
+        <v>20.8</v>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (0.90-1.90)</t>
+          <t>ratio=1.73 (0.90-2.62)</t>
         </is>
       </c>
       <c r="I65" s="8" t="n"/>
@@ -2664,7 +2664,7 @@
         <v>40</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.12 (0.50-1.60)</t>
+          <t>ratio=1.00 (0.50-1.60)</t>
         </is>
       </c>
       <c r="I68" s="8" t="n"/>
@@ -2817,7 +2817,7 @@
         <v>2</v>
       </c>
       <c r="F73" s="10" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (n=2)</t>
+          <t>ratio=2.50 (n=2)</t>
         </is>
       </c>
       <c r="I73" s="8" t="n"/>
@@ -2924,7 +2924,7 @@
         <v>4</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.75 (0.33-2.25)</t>
+          <t>ratio=2.12 (1.50-4.50)</t>
         </is>
       </c>
       <c r="I76" s="8" t="n"/>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="F78" s="1" t="n">
-        <v>397.9</v>
+        <v>383.2</v>
       </c>
     </row>
   </sheetData>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-039, 25-025, 25-037, 23-098, 25-026</t>
+          <t>25-025, 25-039, 25-037, 25-026, 25-087</t>
         </is>
       </c>
     </row>
@@ -4885,14 +4885,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25-039</t>
+          <t>25-025</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25-025</t>
+          <t>25-039</t>
         </is>
       </c>
     </row>
@@ -4906,14 +4906,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23-098</t>
+          <t>25-026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25-026</t>
+          <t>25-087</t>
         </is>
       </c>
     </row>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ratio=1.10 (1.08-1.20)</t>
+          <t>ratio=1.10 (1.00-1.20)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025</t>
+          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
+          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5089,12 +5089,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-039</t>
+          <t>25-087, 25-039</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
+          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
+          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
+          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
+          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5239,12 +5239,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ratio=2.00 (1.00-2.00)</t>
+          <t>ratio=2.00 (1.25-2.00)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
+          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5269,12 +5269,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ratio=1.06 (0.86-1.50)</t>
+          <t>ratio=1.06 (0.29-1.50)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
+          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>18.3</v>
+        <v>20</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ratio=0.92 (0.79-1.10)</t>
+          <t>ratio=1.00 (0.79-1.33)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025</t>
+          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
+          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5359,12 +5359,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.00)</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
+          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-037, 25-026, 25-025, 23-098</t>
+          <t>25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5445,12 +5445,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.67-1.09)</t>
+          <t>ratio=0.75 (0.67-1.50)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
+          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5466,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>21.4</v>
+        <v>20</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5475,12 +5475,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ratio=1.07 (0.62-1.36)</t>
+          <t>ratio=1.00 (0.62-1.36)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
+          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5496,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ratio=0.69 (0.56-1.20)</t>
+          <t>ratio=0.61 (0.56-0.78)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25-037, 25-026, 25-025, 23-098</t>
+          <t>25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
+          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5582,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5591,12 +5591,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ratio=0.83 (0.50-1.17)</t>
+          <t>ratio=0.58 (0.50-1.17)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
+          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5612,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5621,12 +5621,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ratio=0.94 (0.58-1.19)</t>
+          <t>ratio=0.88 (0.33-1.19)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
+          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5681,12 +5681,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ratio=0.83 (0.83-0.88)</t>
+          <t>ratio=0.83 (0.83-0.83)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25-037, 25-026, 25-025, 23-098</t>
+          <t>25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>13.2</v>
+        <v>10.5</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5763,12 +5763,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.38-1.15)</t>
+          <t>ratio=0.70 (0.38-1.15)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
+          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>6.9</v>
+        <v>5</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ratio=1.38 (0.75-2.40)</t>
+          <t>ratio=1.00 (0.75-1.75)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>25-037, 25-026, 25-025, 23-098</t>
+          <t>25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ratio=1.38 (1.12-1.60)</t>
+          <t>ratio=1.25 (1.12-1.50)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>25-037, 25-026, 25-025, 23-098</t>
+          <t>25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5969,12 +5969,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.62-1.33)</t>
+          <t>ratio=1.00 (0.33-1.33)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
+          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>14</v>
+        <v>16.8</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.64-1.43)</t>
+          <t>ratio=1.20 (0.64-1.43)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
+          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6029,12 +6029,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ratio=1.50 (0.50-3.25)</t>
+          <t>ratio=1.00 (0.50-2.00)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
+          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>27.3</v>
+        <v>13.9</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6059,12 +6059,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ratio=0.70 (n=1)</t>
+          <t>ratio=0.36 (n=1)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>23-098</t>
+          <t>25-087</t>
         </is>
       </c>
     </row>
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6089,12 +6089,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ratio=0.71 (n=2)</t>
+          <t>ratio=0.67 (n=1)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>25-037, 23-098</t>
+          <t>25-037</t>
         </is>
       </c>
     </row>
@@ -6119,12 +6119,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ratio=0.43 (0.36-0.73)</t>
+          <t>ratio=0.43 (0.33-0.73)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
+          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -6149,12 +6149,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ratio=0.55 (0.33-0.72)</t>
+          <t>ratio=0.55 (0.30-0.72)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
+          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6170,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6179,12 +6179,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ratio=0.71 (0.50-0.75)</t>
+          <t>ratio=0.75 (0.67-1.00)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>25-039, 25-026, 25-025, 23-098</t>
+          <t>25-087, 25-039, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
+          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6256,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6265,12 +6265,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.50-1.00)</t>
+          <t>ratio=0.75 (0.50-1.00)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>25-037, 25-026, 25-025, 23-098</t>
+          <t>25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6373,12 +6373,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ratio=3.00 (0.50-4.12)</t>
+          <t>ratio=2.81 (0.50-4.12)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
+          <t>25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>15</v>
+        <v>20.8</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6403,12 +6403,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ratio=1.25 (0.90-1.90)</t>
+          <t>ratio=1.73 (0.90-2.62)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
+          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6476,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6485,12 +6485,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ratio=1.12 (0.50-1.60)</t>
+          <t>ratio=1.00 (0.50-1.60)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025, 23-098</t>
+          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
         </is>
       </c>
     </row>
@@ -6584,7 +6584,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6593,12 +6593,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ratio=1.25 (n=2)</t>
+          <t>ratio=2.50 (n=2)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>25-039, 23-098</t>
+          <t>25-087, 25-039</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6679,12 +6679,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ratio=1.75 (0.33-2.25)</t>
+          <t>ratio=2.12 (1.50-4.50)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>25-039, 25-026, 25-025, 23-098</t>
+          <t>25-087, 25-039, 25-026, 25-025</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-085 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-085 GENERATED BUILD PLAN.xlsx
@@ -53,7 +53,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -76,12 +76,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -109,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,7 +117,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -543,7 +536,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-025, 25-039, 25-037, 25-026, 25-087</t>
+          <t>25-037, 25-026, 25-025, 25-039, 25-087</t>
         </is>
       </c>
     </row>
@@ -638,12 +631,12 @@
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -671,12 +664,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -721,7 +714,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -730,7 +723,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.10 (1.00-1.20)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -758,7 +751,7 @@
         <v>6</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>8.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -767,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.36 (0.29-1.82)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -794,17 +787,17 @@
       <c r="E11" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="F11" s="10" t="n">
-        <v>9</v>
+      <c r="F11" s="9" t="n">
+        <v>2.4</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -832,7 +825,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -841,7 +834,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -869,7 +862,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -878,7 +871,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -906,7 +899,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -915,7 +908,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -943,7 +936,7 @@
         <v>4</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -952,7 +945,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.00-2.00)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -980,7 +973,7 @@
         <v>4</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
@@ -989,7 +982,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.00 (1.25-2.00)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="I16" s="8" t="n"/>
@@ -1034,7 +1027,7 @@
         <v>40</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>42.5</v>
+        <v>36.7</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
@@ -1043,7 +1036,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.06 (0.29-1.50)</t>
+          <t>group_total:45h</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1071,7 +1064,7 @@
         <v>20</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>20</v>
+        <v>8.5</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1080,7 +1073,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.79-1.33)</t>
+          <t>group_total:45h</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1125,7 +1118,7 @@
         <v>8</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1134,7 +1127,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.75-1.10)</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1179,7 +1172,7 @@
         <v>2</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1188,7 +1181,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1216,7 +1209,7 @@
         <v>3</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
@@ -1225,7 +1218,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1270,12 +1263,12 @@
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1303,7 +1296,7 @@
         <v>28</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>21</v>
+        <v>19.3</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1312,7 +1305,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.67-1.50)</t>
+          <t>group_total:37h</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1340,7 +1333,7 @@
         <v>20</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1349,7 +1342,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.62-1.36)</t>
+          <t>group_total:37h</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1394,7 +1387,7 @@
         <v>12</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>7.3</v>
+        <v>5.7</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
@@ -1403,7 +1396,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.61 (0.56-0.78)</t>
+          <t>group_total:28h</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1431,12 +1424,12 @@
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1464,7 +1457,7 @@
         <v>2</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1473,7 +1466,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.50 (1.00-5.00)</t>
+          <t>group_total:28h</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1501,7 +1494,7 @@
         <v>4</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1510,7 +1503,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.58 (0.50-1.17)</t>
+          <t>group_total:28h</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1538,7 +1531,7 @@
         <v>8</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>7</v>
+        <v>9.9</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
@@ -1547,7 +1540,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.33-1.19)</t>
+          <t>group_total:28h</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1575,7 +1568,7 @@
         <v>6</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1584,7 +1577,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.50 (0.50-0.67)</t>
+          <t>group_total:28h</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1629,7 +1622,7 @@
         <v>8</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>6.7</v>
+        <v>13.8</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -1638,7 +1631,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.83 (0.83-0.83)</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1683,12 +1676,12 @@
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1716,7 +1709,7 @@
         <v>15</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>10.5</v>
+        <v>17.6</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1725,7 +1718,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.70 (0.38-1.15)</t>
+          <t>group_total:88h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1753,7 +1746,7 @@
         <v>12</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>16</v>
+        <v>10.2</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -1762,7 +1755,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.33 (0.67-1.67)</t>
+          <t>group_total:88h</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1790,7 +1783,7 @@
         <v>10</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
@@ -1799,7 +1792,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.17 (0.33-2.00)</t>
+          <t>group_total:88h</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1827,7 +1820,7 @@
         <v>5</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1836,7 +1829,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-1.75)</t>
+          <t>group_total:88h</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1864,7 +1857,7 @@
         <v>6</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>7.5</v>
+        <v>4.7</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1873,7 +1866,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (1.12-1.50)</t>
+          <t>group_total:88h</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1901,7 +1894,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
@@ -1910,7 +1903,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.83-1.00)</t>
+          <t>group_total:88h</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1938,12 +1931,12 @@
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1971,7 +1964,7 @@
         <v>9</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1980,7 +1973,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.33-1.33)</t>
+          <t>group_total:88h</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2008,7 +2001,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>16.8</v>
+        <v>24.4</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -2017,7 +2010,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.20 (0.64-1.43)</t>
+          <t>group_total:88h</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2044,17 +2037,17 @@
       <c r="E49" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F49" s="9" t="n">
+      <c r="F49" s="10" t="n">
         <v>2</v>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-2.00)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2098,17 +2091,17 @@
       <c r="E51" s="8" t="n">
         <v>39</v>
       </c>
-      <c r="F51" s="10" t="n">
-        <v>13.9</v>
+      <c r="F51" s="9" t="n">
+        <v>17.5</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.36 (n=1)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2135,17 +2128,17 @@
       <c r="E52" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F52" s="10" t="n">
-        <v>3.3</v>
+      <c r="F52" s="9" t="n">
+        <v>2.5</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.67 (n=1)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2173,7 +2166,7 @@
         <v>5</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>2.2</v>
+        <v>10.9</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
@@ -2182,7 +2175,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.43 (0.33-0.73)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="I53" s="8" t="n"/>
@@ -2210,7 +2203,7 @@
         <v>16</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>8.699999999999999</v>
+        <v>21.6</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -2219,7 +2212,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.55 (0.30-0.72)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2247,7 +2240,7 @@
         <v>6</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
@@ -2256,7 +2249,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.67-1.00)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2284,12 +2277,12 @@
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2317,7 +2310,7 @@
         <v>1</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
@@ -2326,7 +2319,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.00)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="I57" s="8" t="n"/>
@@ -2371,7 +2364,7 @@
         <v>1</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
@@ -2380,7 +2373,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.50-1.00)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2408,12 +2401,12 @@
       <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2441,12 +2434,12 @@
       <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I61" s="8" t="n"/>
@@ -2474,12 +2467,12 @@
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2524,7 +2517,7 @@
         <v>2</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
@@ -2533,7 +2526,7 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.81 (0.50-4.12)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="I64" s="8" t="n"/>
@@ -2561,7 +2554,7 @@
         <v>12</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>20.8</v>
+        <v>24.3</v>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
@@ -2570,7 +2563,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.73 (0.90-2.62)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="I65" s="8" t="n"/>
@@ -2598,12 +2591,12 @@
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -2631,12 +2624,12 @@
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -2664,7 +2657,7 @@
         <v>40</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
@@ -2673,7 +2666,7 @@
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.60)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="I68" s="8" t="n"/>
@@ -2701,12 +2694,12 @@
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I69" s="8" t="n"/>
@@ -2734,12 +2727,12 @@
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I70" s="8" t="n"/>
@@ -2767,12 +2760,12 @@
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I71" s="8" t="n"/>
@@ -2816,17 +2809,17 @@
       <c r="E73" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F73" s="10" t="n">
-        <v>5</v>
+      <c r="F73" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.50 (n=2)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="I73" s="8" t="n"/>
@@ -2853,17 +2846,17 @@
       <c r="E74" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F74" s="11" t="n">
-        <v>2</v>
+      <c r="F74" s="9" t="n">
+        <v>1.2</v>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="I74" s="8" t="n"/>
@@ -2891,12 +2884,12 @@
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I75" s="8" t="n"/>
@@ -2924,7 +2917,7 @@
         <v>4</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>8.5</v>
+        <v>10.1</v>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
@@ -2933,7 +2926,7 @@
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.12 (1.50-4.50)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="I76" s="8" t="n"/>
@@ -2947,7 +2940,7 @@
         </is>
       </c>
       <c r="F78" s="1" t="n">
-        <v>383.2</v>
+        <v>419.5</v>
       </c>
     </row>
   </sheetData>
@@ -3015,7 +3008,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-025, 25-039, 25-037, 25-026, 25-087</t>
+          <t>25-037, 25-026, 25-025, 25-039, 25-087</t>
         </is>
       </c>
     </row>
@@ -4885,28 +4878,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25-025</t>
+          <t>25-037</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25-039</t>
+          <t>25-026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25-037</t>
+          <t>25-025</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25-026</t>
+          <t>25-039</t>
         </is>
       </c>
     </row>
@@ -4972,15 +4965,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4998,15 +4995,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5020,7 +5021,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5029,12 +5030,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ratio=1.10 (1.00-1.20)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5051,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5059,12 +5060,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ratio=1.36 (0.29-1.82)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5080,21 +5081,21 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>2.4</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-087, 25-039</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5111,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5119,12 +5120,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5141,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5149,12 +5150,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5170,7 +5171,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5179,12 +5180,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5200,7 +5201,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5209,12 +5210,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.00-2.00)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5230,7 +5231,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5239,12 +5240,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ratio=2.00 (1.25-2.00)</t>
+          <t>group_total:36h</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5260,7 +5261,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>42.5</v>
+        <v>36.7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5269,12 +5270,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ratio=1.06 (0.29-1.50)</t>
+          <t>group_total:45h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5291,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>20</v>
+        <v>8.5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5299,12 +5300,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.79-1.33)</t>
+          <t>group_total:45h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5321,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5329,12 +5330,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.75-1.10)</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
+          <t>model(SUPPORTS)</t>
         </is>
       </c>
     </row>
@@ -5350,7 +5351,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -5359,12 +5360,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5381,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5389,12 +5390,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-037, 25-026, 25-025</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -5414,15 +5415,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5436,7 +5441,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>21</v>
+        <v>19.3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5445,12 +5450,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.67-1.50)</t>
+          <t>group_total:37h</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -5466,7 +5471,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5475,12 +5480,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.62-1.36)</t>
+          <t>group_total:37h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5501,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7.3</v>
+        <v>5.7</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5505,12 +5510,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ratio=0.61 (0.56-0.78)</t>
+          <t>group_total:28h</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25-037, 25-026, 25-025</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5530,15 +5535,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5552,7 +5561,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5561,12 +5570,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ratio=2.50 (1.00-5.00)</t>
+          <t>group_total:28h</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5591,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5591,12 +5600,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ratio=0.58 (0.50-1.17)</t>
+          <t>group_total:28h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5621,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>9.9</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5621,12 +5630,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.33-1.19)</t>
+          <t>group_total:28h</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5642,7 +5651,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5651,12 +5660,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ratio=0.50 (0.50-0.67)</t>
+          <t>group_total:28h</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5681,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6.7</v>
+        <v>13.8</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5681,12 +5690,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ratio=0.83 (0.83-0.83)</t>
+          <t>group_total:14h</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25-037, 25-026, 25-025</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5706,15 +5715,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5732,15 +5745,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5754,7 +5771,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>10.5</v>
+        <v>17.6</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5763,12 +5780,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ratio=0.70 (0.38-1.15)</t>
+          <t>group_total:88h</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5801,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>16</v>
+        <v>10.2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5793,12 +5810,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ratio=1.33 (0.67-1.67)</t>
+          <t>group_total:88h</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-025</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5814,7 +5831,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5823,12 +5840,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ratio=1.17 (0.33-2.00)</t>
+          <t>group_total:88h</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5861,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5853,12 +5870,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.75-1.75)</t>
+          <t>group_total:88h</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>25-037, 25-026, 25-025</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5891,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7.5</v>
+        <v>4.7</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5883,12 +5900,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ratio=1.25 (1.12-1.50)</t>
+          <t>group_total:88h</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>25-037, 25-026, 25-025</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5921,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5913,12 +5930,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.83-1.00)</t>
+          <t>group_total:88h</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5938,15 +5955,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5960,7 +5981,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5969,12 +5990,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.33-1.33)</t>
+          <t>group_total:88h</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -5990,7 +6011,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>16.8</v>
+        <v>24.4</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5999,12 +6020,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ratio=1.20 (0.64-1.43)</t>
+          <t>group_total:88h</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6024,17 +6045,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-2.00)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -6050,21 +6071,21 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>13.9</v>
+        <v>17.5</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ratio=0.36 (n=1)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>25-087</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6080,21 +6101,21 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ratio=0.67 (n=1)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>25-037</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6110,7 +6131,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2.2</v>
+        <v>10.9</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6119,12 +6140,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ratio=0.43 (0.33-0.73)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6140,7 +6161,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>8.699999999999999</v>
+        <v>21.6</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6149,12 +6170,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ratio=0.55 (0.30-0.72)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6170,7 +6191,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6179,12 +6200,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.67-1.00)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-026, 25-025</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6204,15 +6225,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6226,7 +6251,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6235,12 +6260,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.00)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6256,7 +6281,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6265,12 +6290,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.50-1.00)</t>
+          <t>group_total:63h</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>25-037, 25-026, 25-025</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6290,15 +6315,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6316,15 +6345,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6342,15 +6375,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6364,7 +6401,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6373,12 +6410,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ratio=2.81 (0.50-4.12)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>25-039, 25-037, 25-026, 25-025</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6394,7 +6431,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>20.8</v>
+        <v>24.3</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6403,12 +6440,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ratio=1.73 (0.90-2.62)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6428,15 +6465,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6454,15 +6495,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6476,7 +6521,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6485,12 +6530,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.60)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-037, 25-026, 25-025</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6510,15 +6555,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6536,15 +6585,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6562,15 +6615,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6584,21 +6641,21 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ratio=2.50 (n=2)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>25-087, 25-039</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6614,21 +6671,21 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6648,15 +6705,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6670,7 +6731,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>8.5</v>
+        <v>10.1</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6679,12 +6740,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ratio=2.12 (1.50-4.50)</t>
+          <t>group_total:91h</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>25-087, 25-039, 25-026, 25-025</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-085 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-085 GENERATED BUILD PLAN.xlsx
@@ -714,7 +714,7 @@
         <v>4</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -751,7 +751,7 @@
         <v>6</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>15.5</v>
+        <v>14.6</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -788,7 +788,7 @@
         <v>9</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -825,7 +825,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -871,7 +871,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -899,7 +899,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -936,7 +936,7 @@
         <v>4</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -973,7 +973,7 @@
         <v>4</v>
       </c>
       <c r="F16" s="9" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G16" s="8" t="inlineStr">
         <is>
@@ -982,7 +982,7 @@
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="I16" s="8" t="n"/>
@@ -1027,7 +1027,7 @@
         <v>40</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>36.7</v>
+        <v>41.1</v>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="H18" s="8" t="inlineStr">
         <is>
-          <t>group_total:45h</t>
+          <t>group_total:51h</t>
         </is>
       </c>
       <c r="I18" s="8" t="n"/>
@@ -1064,7 +1064,7 @@
         <v>20</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>group_total:45h</t>
+          <t>group_total:51h</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1118,7 +1118,7 @@
         <v>8</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>group_total:7h</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1172,7 +1172,7 @@
         <v>2</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1209,7 +1209,7 @@
         <v>3</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1296,7 +1296,7 @@
         <v>28</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>19.3</v>
+        <v>20.4</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>group_total:37h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1333,7 +1333,7 @@
         <v>20</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>17.8</v>
+        <v>18.8</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>group_total:37h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1387,7 +1387,7 @@
         <v>12</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>group_total:28h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1457,7 +1457,7 @@
         <v>2</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>group_total:28h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1494,7 +1494,7 @@
         <v>4</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>group_total:28h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1531,7 +1531,7 @@
         <v>8</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>9.9</v>
+        <v>9.4</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>group_total:28h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1568,7 +1568,7 @@
         <v>6</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>group_total:28h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1622,7 +1622,7 @@
         <v>8</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>13.8</v>
+        <v>7.8</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>group_total:14h</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1709,7 +1709,7 @@
         <v>15</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>17.6</v>
+        <v>19</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>group_total:88h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1746,7 +1746,7 @@
         <v>12</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>10.2</v>
+        <v>11</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>group_total:88h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1783,7 +1783,7 @@
         <v>10</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>group_total:88h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1820,7 +1820,7 @@
         <v>5</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>group_total:88h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1857,7 +1857,7 @@
         <v>6</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>group_total:88h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1894,7 +1894,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="9" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="G45" s="8" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>group_total:88h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1964,7 +1964,7 @@
         <v>9</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>10.5</v>
+        <v>11.3</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>group_total:88h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -2001,7 +2001,7 @@
         <v>14</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>24.4</v>
+        <v>26.3</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>group_total:88h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2092,7 +2092,7 @@
         <v>39</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>17.5</v>
+        <v>15.8</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:57h</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2129,7 +2129,7 @@
         <v>5</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:57h</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2166,7 +2166,7 @@
         <v>5</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>10.9</v>
+        <v>9.9</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:57h</t>
         </is>
       </c>
       <c r="I53" s="8" t="n"/>
@@ -2203,7 +2203,7 @@
         <v>16</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>21.6</v>
+        <v>19.6</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:57h</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2240,7 +2240,7 @@
         <v>6</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:57h</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2310,7 +2310,7 @@
         <v>1</v>
       </c>
       <c r="F57" s="9" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G57" s="8" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:57h</t>
         </is>
       </c>
       <c r="I57" s="8" t="n"/>
@@ -2364,7 +2364,7 @@
         <v>1</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:57h</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2517,7 +2517,7 @@
         <v>2</v>
       </c>
       <c r="F64" s="9" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="G64" s="8" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:103h</t>
         </is>
       </c>
       <c r="I64" s="8" t="n"/>
@@ -2554,7 +2554,7 @@
         <v>12</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>24.3</v>
+        <v>27.6</v>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:103h</t>
         </is>
       </c>
       <c r="I65" s="8" t="n"/>
@@ -2657,7 +2657,7 @@
         <v>40</v>
       </c>
       <c r="F68" s="9" t="n">
-        <v>42</v>
+        <v>47.6</v>
       </c>
       <c r="G68" s="8" t="inlineStr">
         <is>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:103h</t>
         </is>
       </c>
       <c r="I68" s="8" t="n"/>
@@ -2810,7 +2810,7 @@
         <v>2</v>
       </c>
       <c r="F73" s="9" t="n">
-        <v>8</v>
+        <v>9.1</v>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:103h</t>
         </is>
       </c>
       <c r="I73" s="8" t="n"/>
@@ -2847,7 +2847,7 @@
         <v>2</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:103h</t>
         </is>
       </c>
       <c r="I74" s="8" t="n"/>
@@ -2917,7 +2917,7 @@
         <v>4</v>
       </c>
       <c r="F76" s="9" t="n">
-        <v>10.1</v>
+        <v>11.5</v>
       </c>
       <c r="G76" s="8" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:103h</t>
         </is>
       </c>
       <c r="I76" s="8" t="n"/>
@@ -2940,7 +2940,7 @@
         </is>
       </c>
       <c r="F78" s="1" t="n">
-        <v>419.5</v>
+        <v>427.6</v>
       </c>
     </row>
   </sheetData>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -5051,7 +5051,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>15.5</v>
+        <v>14.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -5081,7 +5081,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -5201,7 +5201,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>group_total:36h</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>36.7</v>
+        <v>41.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>group_total:45h</t>
+          <t>group_total:51h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -5291,7 +5291,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>group_total:45h</t>
+          <t>group_total:51h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>group_total:7h</t>
+          <t>group_total:6h</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5351,7 +5351,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5381,7 +5381,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>group_total:10h</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5441,7 +5441,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>19.3</v>
+        <v>20.4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>group_total:37h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>17.8</v>
+        <v>18.8</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>group_total:37h</t>
+          <t>group_total:39h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>group_total:28h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -5561,7 +5561,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>group_total:28h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -5591,7 +5591,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>group_total:28h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -5621,7 +5621,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>9.9</v>
+        <v>9.4</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>group_total:28h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -5651,7 +5651,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>group_total:28h</t>
+          <t>group_total:26h</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -5681,7 +5681,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>13.8</v>
+        <v>7.8</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>group_total:14h</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -5771,7 +5771,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>17.6</v>
+        <v>19</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>group_total:88h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>10.2</v>
+        <v>11</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>group_total:88h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>group_total:88h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5861,7 +5861,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>group_total:88h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5891,7 +5891,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>group_total:88h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>group_total:88h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>10.5</v>
+        <v>11.3</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>group_total:88h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>24.4</v>
+        <v>26.3</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>group_total:88h</t>
+          <t>group_total:94h</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>17.5</v>
+        <v>15.8</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:57h</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -6101,7 +6101,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:57h</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>10.9</v>
+        <v>9.9</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:57h</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6161,7 +6161,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>21.6</v>
+        <v>19.6</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6170,7 +6170,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:57h</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6191,7 +6191,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:57h</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:57h</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6281,7 +6281,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>group_total:63h</t>
+          <t>group_total:57h</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6401,7 +6401,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:103h</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6431,7 +6431,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>24.3</v>
+        <v>27.6</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:103h</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>42</v>
+        <v>47.6</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:103h</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6641,7 +6641,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>8</v>
+        <v>9.1</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:103h</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:103h</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>10.1</v>
+        <v>11.5</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>group_total:91h</t>
+          <t>group_total:103h</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
